--- a/tools/importer/reports/import-figma.report.xlsx
+++ b/tools/importer/reports/import-figma.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="284">
   <si>
     <t>_reportFile</t>
   </si>
@@ -263,6 +263,66 @@
   </si>
   <si>
     <t>https://lsa.umich.edu/english/undergraduate.html</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/footer.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/footer</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:13.186Z</t>
+  </si>
+  <si>
+    <t>LSA Design System – Footer</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/footer.html</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/index.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/index</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:36:57.655Z</t>
+  </si>
+  <si>
+    <t>LSA Design System</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/index.html</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/nav.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/nav</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:08.102Z</t>
+  </si>
+  <si>
+    <t>LSA Design System – Navigation</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/nav.html</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/style-guide.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/style-guide</t>
+  </si>
+  <si>
+    <t>2026-10-26T18:37:04.346Z</t>
+  </si>
+  <si>
+    <t>LSA Design System – Style Guide</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/style-guide.html</t>
   </si>
   <si>
     <t>en/prospective-students/graduate.report.json</t>
@@ -1191,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -1656,7 +1716,7 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1664,142 +1724,142 @@
       <c r="D15" t="s">
         <v>85</v>
       </c>
-      <c r="E15" t="s">
-        <v>12</v>
+      <c r="E15">
+        <v>2</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
         <v>86</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>87</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>88</v>
-      </c>
-      <c r="J15" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
         <v>90</v>
       </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>92</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>93</v>
-      </c>
-      <c r="J16" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
         <v>95</v>
       </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>97</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>98</v>
-      </c>
-      <c r="J17" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
         <v>100</v>
       </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
         <v>101</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>102</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>103</v>
-      </c>
-      <c r="J18" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
         <v>105</v>
       </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
         <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>86</v>
       </c>
       <c r="H19" t="s">
         <v>107</v>
@@ -1816,36 +1876,36 @@
         <v>110</v>
       </c>
       <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
         <v>111</v>
       </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" t="s">
         <v>112</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>113</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>114</v>
-      </c>
-      <c r="J20" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -1854,103 +1914,103 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
         <v>117</v>
       </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>118</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>119</v>
-      </c>
-      <c r="J21" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
         <v>121</v>
       </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" t="s">
         <v>122</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>123</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>124</v>
-      </c>
-      <c r="J22" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
         <v>126</v>
       </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" t="s">
         <v>127</v>
       </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>128</v>
       </c>
-      <c r="I23" t="s">
-        <v>82</v>
-      </c>
       <c r="J23" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -1959,30 +2019,30 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -1991,30 +2051,30 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -2023,30 +2083,30 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I26" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J26" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -2055,21 +2115,21 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
@@ -2078,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -2087,24 +2147,24 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="H28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J28" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" t="s">
         <v>153</v>
-      </c>
-      <c r="B29" t="s">
-        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2119,7 +2179,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
         <v>155</v>
@@ -2136,7 +2196,7 @@
         <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2151,7 +2211,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H30" t="s">
         <v>160</v>
@@ -2168,7 +2228,7 @@
         <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2183,7 +2243,7 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
         <v>165</v>
@@ -2215,7 +2275,7 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H32" t="s">
         <v>170</v>
@@ -2247,7 +2307,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H33" t="s">
         <v>175</v>
@@ -2279,7 +2339,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H34" t="s">
         <v>180</v>
@@ -2311,7 +2371,7 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H35" t="s">
         <v>185</v>
@@ -2343,7 +2403,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H36" t="s">
         <v>190</v>
@@ -2375,7 +2435,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -2407,7 +2467,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H38" t="s">
         <v>200</v>
@@ -2439,7 +2499,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H39" t="s">
         <v>205</v>
@@ -2471,7 +2531,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H40" t="s">
         <v>210</v>
@@ -2503,30 +2563,30 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H41" t="s">
         <v>215</v>
       </c>
       <c r="I41" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="J41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
         <v>12</v>
@@ -2535,21 +2595,21 @@
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
@@ -2558,7 +2618,7 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
         <v>12</v>
@@ -2567,21 +2627,21 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J43" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
@@ -2590,7 +2650,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
@@ -2599,30 +2659,30 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I44" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J44" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E45" t="s">
         <v>12</v>
@@ -2631,13 +2691,13 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="H45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I45" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="J45" t="s">
         <v>236</v>
@@ -2663,21 +2723,21 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="H46" t="s">
         <v>239</v>
       </c>
       <c r="I46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J46" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -2686,7 +2746,7 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
@@ -2695,30 +2755,30 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H47" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J47" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E48" t="s">
         <v>12</v>
@@ -2727,30 +2787,30 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H48" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J48" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
@@ -2759,53 +2819,53 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="H49" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I49" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J49" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>257</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" t="s">
+        <v>259</v>
+      </c>
+      <c r="I50" t="s">
         <v>255</v>
       </c>
-      <c r="B50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="J50" t="s">
         <v>256</v>
-      </c>
-      <c r="E50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" t="s">
-        <v>86</v>
-      </c>
-      <c r="H50" t="s">
-        <v>257</v>
-      </c>
-      <c r="I50" t="s">
-        <v>225</v>
-      </c>
-      <c r="J50" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -2814,7 +2874,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E51" t="s">
         <v>12</v>
@@ -2823,16 +2883,144 @@
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J51" t="s">
-        <v>263</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>265</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" t="s">
+        <v>267</v>
+      </c>
+      <c r="I52" t="s">
+        <v>268</v>
+      </c>
+      <c r="J52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>270</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>271</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>106</v>
+      </c>
+      <c r="H53" t="s">
+        <v>272</v>
+      </c>
+      <c r="I53" t="s">
+        <v>273</v>
+      </c>
+      <c r="J53" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>275</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" t="s">
+        <v>277</v>
+      </c>
+      <c r="I54" t="s">
+        <v>245</v>
+      </c>
+      <c r="J54" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>279</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>280</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" t="s">
+        <v>281</v>
+      </c>
+      <c r="I55" t="s">
+        <v>282</v>
+      </c>
+      <c r="J55" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-figma.report.xlsx
+++ b/tools/importer/reports/import-figma.report.xlsx
@@ -286,7 +286,7 @@
     <t>en/lsa-figma/index</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:57.655Z</t>
+    <t>2026-10-26T19:37:40.260Z</t>
   </si>
   <si>
     <t>LSA Design System</t>
@@ -316,7 +316,7 @@
     <t>en/lsa-figma/style-guide</t>
   </si>
   <si>
-    <t>2026-10-26T18:37:04.346Z</t>
+    <t>2026-10-26T19:37:44.774Z</t>
   </si>
   <si>
     <t>LSA Design System – Style Guide</t>

--- a/tools/importer/reports/import-figma.report.xlsx
+++ b/tools/importer/reports/import-figma.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="304">
   <si>
     <t>_reportFile</t>
   </si>
@@ -265,13 +265,28 @@
     <t>https://lsa.umich.edu/english/undergraduate.html</t>
   </si>
   <si>
+    <t>en/lsa-figma/faculty-and-staff.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/faculty-and-staff</t>
+  </si>
+  <si>
+    <t>2026-10-26T20:03:12.317Z</t>
+  </si>
+  <si>
+    <t>Faculty And Staff</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/faculty-and-staff.html</t>
+  </si>
+  <si>
     <t>en/lsa-figma/footer.report.json</t>
   </si>
   <si>
     <t>en/lsa-figma/footer</t>
   </si>
   <si>
-    <t>2026-10-26T18:37:13.186Z</t>
+    <t>2026-10-26T19:55:11.374Z</t>
   </si>
   <si>
     <t>LSA Design System – Footer</t>
@@ -286,7 +301,7 @@
     <t>en/lsa-figma/index</t>
   </si>
   <si>
-    <t>2026-10-26T19:37:40.260Z</t>
+    <t>2026-10-26T20:03:00.892Z</t>
   </si>
   <si>
     <t>LSA Design System</t>
@@ -295,13 +310,28 @@
     <t>http://localhost:8093/lsa-figma/index.html</t>
   </si>
   <si>
+    <t>en/lsa-figma/lite-mode.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/lite-mode</t>
+  </si>
+  <si>
+    <t>2026-10-26T20:03:20.588Z</t>
+  </si>
+  <si>
+    <t>Lite Mode</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/lite-mode.html</t>
+  </si>
+  <si>
     <t>en/lsa-figma/nav.report.json</t>
   </si>
   <si>
     <t>en/lsa-figma/nav</t>
   </si>
   <si>
-    <t>2026-10-26T18:37:08.102Z</t>
+    <t>2026-10-26T19:55:06.754Z</t>
   </si>
   <si>
     <t>LSA Design System – Navigation</t>
@@ -310,13 +340,28 @@
     <t>http://localhost:8093/lsa-figma/nav.html</t>
   </si>
   <si>
+    <t>en/lsa-figma/section-nav.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/section-nav</t>
+  </si>
+  <si>
+    <t>2026-10-26T19:55:28.766Z</t>
+  </si>
+  <si>
+    <t>Faculty And Staff – Section navigation</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/section-nav.html</t>
+  </si>
+  <si>
     <t>en/lsa-figma/style-guide.report.json</t>
   </si>
   <si>
     <t>en/lsa-figma/style-guide</t>
   </si>
   <si>
-    <t>2026-10-26T19:37:44.774Z</t>
+    <t>2026-10-26T20:03:06.526Z</t>
   </si>
   <si>
     <t>LSA Design System – Style Guide</t>
@@ -467,6 +512,21 @@
   </si>
   <si>
     <t>2026-10-08T16:13:26.498Z</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/faculty-and-staff/technology-services.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/faculty-and-staff/technology-services</t>
+  </si>
+  <si>
+    <t>2026-10-26T20:03:16.806Z</t>
+  </si>
+  <si>
+    <t>Technology Services</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/faculty-and-staff/technology-services.html</t>
   </si>
   <si>
     <t>en/prospective-students/graduate/applying.report.json</t>
@@ -1251,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -1725,7 +1785,7 @@
         <v>85</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -1757,7 +1817,7 @@
         <v>90</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
@@ -1789,7 +1849,7 @@
         <v>95</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
@@ -1821,7 +1881,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -1844,7 +1904,7 @@
         <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1852,92 +1912,92 @@
       <c r="D19" t="s">
         <v>105</v>
       </c>
-      <c r="E19" t="s">
-        <v>12</v>
+      <c r="E19">
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
         <v>106</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>107</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>108</v>
-      </c>
-      <c r="J19" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
         <v>110</v>
       </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
         <v>111</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>112</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>113</v>
-      </c>
-      <c r="J20" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
         <v>115</v>
       </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
         <v>116</v>
       </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>117</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>118</v>
-      </c>
-      <c r="J21" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
         <v>79</v>
@@ -1946,16 +2006,16 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
         <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>106</v>
       </c>
       <c r="H22" t="s">
         <v>122</v>
@@ -1987,7 +2047,7 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H23" t="s">
         <v>127</v>
@@ -2004,68 +2064,68 @@
         <v>130</v>
       </c>
       <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
         <v>131</v>
       </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" t="s">
         <v>132</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>133</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>134</v>
-      </c>
-      <c r="J24" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" t="s">
         <v>137</v>
       </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>138</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>139</v>
-      </c>
-      <c r="J25" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
@@ -2074,33 +2134,33 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" t="s">
         <v>142</v>
       </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>143</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>144</v>
-      </c>
-      <c r="J26" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" t="s">
         <v>146</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2115,21 +2175,21 @@
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H27" t="s">
         <v>148</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
@@ -2138,7 +2198,7 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -2147,30 +2207,30 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J28" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -2179,30 +2239,30 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="H29" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I29" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J29" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -2211,30 +2271,30 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="H30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I30" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -2243,56 +2303,56 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I31" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
         <v>168</v>
       </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" t="s">
         <v>169</v>
       </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" t="s">
-        <v>106</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>170</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>171</v>
-      </c>
-      <c r="J32" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" t="s">
         <v>173</v>
-      </c>
-      <c r="B33" t="s">
-        <v>20</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2307,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>175</v>
@@ -2324,7 +2384,7 @@
         <v>178</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2339,7 +2399,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
         <v>180</v>
@@ -2356,7 +2416,7 @@
         <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2371,7 +2431,7 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
         <v>185</v>
@@ -2403,7 +2463,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H36" t="s">
         <v>190</v>
@@ -2435,7 +2495,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -2467,7 +2527,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H38" t="s">
         <v>200</v>
@@ -2499,7 +2559,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H39" t="s">
         <v>205</v>
@@ -2531,7 +2591,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H40" t="s">
         <v>210</v>
@@ -2563,7 +2623,7 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H41" t="s">
         <v>215</v>
@@ -2595,7 +2655,7 @@
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H42" t="s">
         <v>220</v>
@@ -2627,7 +2687,7 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H43" t="s">
         <v>225</v>
@@ -2659,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H44" t="s">
         <v>230</v>
@@ -2691,30 +2751,30 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H45" t="s">
         <v>235</v>
       </c>
       <c r="I45" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="J45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E46" t="s">
         <v>12</v>
@@ -2723,21 +2783,21 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -2746,7 +2806,7 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
@@ -2755,21 +2815,21 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
@@ -2778,7 +2838,7 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E48" t="s">
         <v>12</v>
@@ -2787,30 +2847,30 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E49" t="s">
         <v>12</v>
@@ -2819,13 +2879,13 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="H49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I49" t="s">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="J49" t="s">
         <v>256</v>
@@ -2851,21 +2911,21 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="H50" t="s">
         <v>259</v>
       </c>
       <c r="I50" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J50" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -2874,7 +2934,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E51" t="s">
         <v>12</v>
@@ -2883,30 +2943,30 @@
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H51" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I51" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J51" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E52" t="s">
         <v>12</v>
@@ -2915,30 +2975,30 @@
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I52" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J52" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E53" t="s">
         <v>12</v>
@@ -2947,53 +3007,53 @@
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="H53" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I53" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J53" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>277</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" t="s">
+        <v>279</v>
+      </c>
+      <c r="I54" t="s">
         <v>275</v>
       </c>
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="J54" t="s">
         <v>276</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" t="s">
-        <v>106</v>
-      </c>
-      <c r="H54" t="s">
-        <v>277</v>
-      </c>
-      <c r="I54" t="s">
-        <v>245</v>
-      </c>
-      <c r="J54" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
@@ -3002,7 +3062,7 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E55" t="s">
         <v>12</v>
@@ -3011,16 +3071,144 @@
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H55" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J55" t="s">
-        <v>283</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>285</v>
+      </c>
+      <c r="B56" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>286</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>291</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" t="s">
+        <v>292</v>
+      </c>
+      <c r="I57" t="s">
+        <v>293</v>
+      </c>
+      <c r="J57" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>296</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>121</v>
+      </c>
+      <c r="H58" t="s">
+        <v>297</v>
+      </c>
+      <c r="I58" t="s">
+        <v>265</v>
+      </c>
+      <c r="J58" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>299</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>300</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>121</v>
+      </c>
+      <c r="H59" t="s">
+        <v>301</v>
+      </c>
+      <c r="I59" t="s">
+        <v>302</v>
+      </c>
+      <c r="J59" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-figma.report.xlsx
+++ b/tools/importer/reports/import-figma.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="309">
   <si>
     <t>_reportFile</t>
   </si>
@@ -368,6 +368,21 @@
   </si>
   <si>
     <t>http://localhost:8093/lsa-figma/style-guide.html</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/why-lsa.report.json</t>
+  </si>
+  <si>
+    <t>en/lsa-figma/why-lsa</t>
+  </si>
+  <si>
+    <t>2026-10-28T16:28:25.878Z</t>
+  </si>
+  <si>
+    <t>Why LSA</t>
+  </si>
+  <si>
+    <t>http://localhost:8093/lsa-figma/why-lsa.html</t>
   </si>
   <si>
     <t>en/prospective-students/graduate.report.json</t>
@@ -1311,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -2000,7 +2015,7 @@
         <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -2008,46 +2023,46 @@
       <c r="D22" t="s">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
+      <c r="E22">
+        <v>2</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" t="s">
         <v>121</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>122</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>123</v>
-      </c>
-      <c r="J22" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
         <v>125</v>
       </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
         <v>126</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>121</v>
       </c>
       <c r="H23" t="s">
         <v>127</v>
@@ -2079,7 +2094,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
         <v>132</v>
@@ -2096,7 +2111,7 @@
         <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -2111,7 +2126,7 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
         <v>137</v>
@@ -2128,7 +2143,7 @@
         <v>140</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2143,7 +2158,7 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H26" t="s">
         <v>142</v>
@@ -2160,39 +2175,39 @@
         <v>145</v>
       </c>
       <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
         <v>146</v>
       </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" t="s">
         <v>147</v>
       </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>148</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>149</v>
-      </c>
-      <c r="J27" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
         <v>151</v>
-      </c>
-      <c r="B28" t="s">
-        <v>20</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2207,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="H28" t="s">
         <v>153</v>
@@ -2239,7 +2254,7 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="H29" t="s">
         <v>158</v>
@@ -2256,7 +2271,7 @@
         <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2277,24 +2292,24 @@
         <v>163</v>
       </c>
       <c r="I30" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="J30" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -2306,45 +2321,45 @@
         <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I31" t="s">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H32" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I32" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J32" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2352,39 +2367,39 @@
         <v>172</v>
       </c>
       <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
         <v>173</v>
       </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" t="s">
         <v>174</v>
       </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>175</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>176</v>
-      </c>
-      <c r="J33" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" t="s">
         <v>178</v>
-      </c>
-      <c r="B34" t="s">
-        <v>173</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2399,7 +2414,7 @@
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
         <v>180</v>
@@ -2416,7 +2431,7 @@
         <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2431,7 +2446,7 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H35" t="s">
         <v>185</v>
@@ -2448,7 +2463,7 @@
         <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2463,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
         <v>190</v>
@@ -2495,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -2527,7 +2542,7 @@
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H38" t="s">
         <v>200</v>
@@ -2559,7 +2574,7 @@
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H39" t="s">
         <v>205</v>
@@ -2591,7 +2606,7 @@
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H40" t="s">
         <v>210</v>
@@ -2623,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H41" t="s">
         <v>215</v>
@@ -2655,7 +2670,7 @@
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H42" t="s">
         <v>220</v>
@@ -2687,7 +2702,7 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H43" t="s">
         <v>225</v>
@@ -2719,7 +2734,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H44" t="s">
         <v>230</v>
@@ -2751,7 +2766,7 @@
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H45" t="s">
         <v>235</v>
@@ -2783,7 +2798,7 @@
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H46" t="s">
         <v>240</v>
@@ -2815,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H47" t="s">
         <v>245</v>
@@ -2847,7 +2862,7 @@
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H48" t="s">
         <v>250</v>
@@ -2879,30 +2894,30 @@
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H49" t="s">
         <v>255</v>
       </c>
       <c r="I49" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="J49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E50" t="s">
         <v>12</v>
@@ -2911,13 +2926,13 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I50" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="J50" t="s">
         <v>261</v>
@@ -2928,7 +2943,7 @@
         <v>262</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -2943,7 +2958,7 @@
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H51" t="s">
         <v>264</v>
@@ -2975,7 +2990,7 @@
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
         <v>269</v>
@@ -2992,7 +3007,7 @@
         <v>272</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3007,7 +3022,7 @@
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
         <v>274</v>
@@ -3045,42 +3060,42 @@
         <v>279</v>
       </c>
       <c r="I54" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J54" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>282</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>283</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" t="s">
+        <v>284</v>
+      </c>
+      <c r="I55" t="s">
         <v>280</v>
       </c>
-      <c r="B55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="J55" t="s">
         <v>281</v>
-      </c>
-      <c r="E55" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s">
-        <v>121</v>
-      </c>
-      <c r="H55" t="s">
-        <v>282</v>
-      </c>
-      <c r="I55" t="s">
-        <v>283</v>
-      </c>
-      <c r="J55" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3088,7 +3103,7 @@
         <v>285</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3103,7 +3118,7 @@
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H56" t="s">
         <v>287</v>
@@ -3120,7 +3135,7 @@
         <v>290</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3135,7 +3150,7 @@
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H57" t="s">
         <v>292</v>
@@ -3167,21 +3182,21 @@
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H58" t="s">
         <v>297</v>
       </c>
       <c r="I58" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="J58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s">
         <v>20</v>
@@ -3190,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
@@ -3199,16 +3214,48 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H59" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I59" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="J59" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>304</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>305</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" t="s">
+        <v>306</v>
+      </c>
+      <c r="I60" t="s">
+        <v>307</v>
+      </c>
+      <c r="J60" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
